--- a/data/trans_dic/P16A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,01</t>
+          <t>7,49; 11,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,55</t>
+          <t>9,21; 13,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,39</t>
+          <t>6,65; 10,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,38</t>
+          <t>6,39; 11,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,3</t>
+          <t>4,56; 7,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,33</t>
+          <t>6,41; 9,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,16</t>
+          <t>5,39; 8,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,65</t>
+          <t>6,69; 9,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,54</t>
+          <t>6,3; 8,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,61</t>
+          <t>8,03; 10,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,06</t>
+          <t>6,43; 9,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 9,69</t>
+          <t>7,06; 9,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,07</t>
+          <t>4,68; 6,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,97</t>
+          <t>7,2; 9,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,9</t>
+          <t>6,48; 8,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,94</t>
+          <t>3,85; 6,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,32</t>
+          <t>4,84; 7,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,32</t>
+          <t>7,55; 10,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,28</t>
+          <t>7,56; 10,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,21</t>
+          <t>4,99; 8,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,72</t>
+          <t>5,03; 6,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 9,58</t>
+          <t>7,78; 9,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,12</t>
+          <t>7,4; 9,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,27</t>
+          <t>4,91; 7,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,81</t>
+          <t>4,49; 8,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 13,7</t>
+          <t>7,39; 14,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,63</t>
+          <t>5,22; 9,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,92</t>
+          <t>6,38; 11,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,53</t>
+          <t>6,9; 12,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,76</t>
+          <t>5,52; 10,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,1</t>
+          <t>6,3; 11,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,11</t>
+          <t>5,76; 8,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,68</t>
+          <t>6,22; 9,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,94</t>
+          <t>6,92; 11,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,69</t>
+          <t>6,3; 9,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,85</t>
+          <t>6,48; 9,63</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,81</t>
+          <t>6,07; 7,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,56</t>
+          <t>8,44; 10,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,8</t>
+          <t>6,79; 8,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,73</t>
+          <t>4,98; 7,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,35</t>
+          <t>5,6; 7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,23</t>
+          <t>7,47; 9,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,33</t>
+          <t>7,32; 9,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,04</t>
+          <t>5,86; 8,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,37</t>
+          <t>6,02; 7,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,63</t>
+          <t>8,19; 9,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,74</t>
+          <t>7,38; 8,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 7,65</t>
+          <t>5,9; 7,65</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77327; 113607</t>
+          <t>77320; 114338</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89692; 131700</t>
+          <t>89513; 128646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48957; 78401</t>
+          <t>50194; 81584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33498; 58511</t>
+          <t>32836; 57798</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>61820; 95942</t>
+          <t>59904; 93619</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85165; 124289</t>
+          <t>85372; 122903</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55723; 91100</t>
+          <t>53584; 89115</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50736; 72511</t>
+          <t>50284; 70994</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149378; 200366</t>
+          <t>147775; 198252</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189699; 244367</t>
+          <t>184892; 240175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113436; 158412</t>
+          <t>112383; 160747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88029; 122652</t>
+          <t>89390; 122347</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80277; 119715</t>
+          <t>79185; 116385</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>142052; 195357</t>
+          <t>141078; 191512</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135151; 184854</t>
+          <t>134523; 183039</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89414; 158900</t>
+          <t>88216; 159361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75605; 116197</t>
+          <t>76831; 116428</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132291; 180835</t>
+          <t>132225; 181750</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>152657; 204453</t>
+          <t>150229; 202622</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112456; 183605</t>
+          <t>111688; 183489</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165825; 220306</t>
+          <t>165116; 220626</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>287345; 355580</t>
+          <t>288682; 359910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300757; 370901</t>
+          <t>300804; 369405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>224546; 329214</t>
+          <t>222308; 324686</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25313; 48589</t>
+          <t>24736; 48615</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33376; 65788</t>
+          <t>35498; 68048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27501; 52678</t>
+          <t>28571; 52759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40409; 77102</t>
+          <t>41287; 76042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33851; 59685</t>
+          <t>32867; 58587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25113; 49239</t>
+          <t>25251; 49210</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34086; 60963</t>
+          <t>34574; 60511</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37753; 60155</t>
+          <t>38057; 59405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62932; 99462</t>
+          <t>63950; 97701</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65029; 102620</t>
+          <t>64918; 105654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67677; 106256</t>
+          <t>69090; 105668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85853; 128797</t>
+          <t>84650; 125911</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>196981; 255794</t>
+          <t>198803; 256265</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>288932; 360290</t>
+          <t>288083; 358811</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>233595; 297332</t>
+          <t>229394; 291825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>176519; 266677</t>
+          <t>171959; 266946</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>187296; 248215</t>
+          <t>189238; 247559</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>263549; 326701</t>
+          <t>264385; 328642</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>261010; 329677</t>
+          <t>258571; 327784</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>211784; 293280</t>
+          <t>213948; 297209</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>405507; 490355</t>
+          <t>400407; 487562</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>569761; 669880</t>
+          <t>569642; 667944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>507693; 603830</t>
+          <t>509886; 601815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>424363; 542774</t>
+          <t>418744; 543066</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,08</t>
+          <t>7,45; 11,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,24</t>
+          <t>9,34; 13,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,82</t>
+          <t>6,41; 10,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 11,25</t>
+          <t>6,03; 10,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,12</t>
+          <t>4,69; 7,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,23</t>
+          <t>6,24; 9,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,96</t>
+          <t>5,66; 9,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,44</t>
+          <t>6,71; 9,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,45</t>
+          <t>6,26; 8,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,43</t>
+          <t>8,12; 10,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,19</t>
+          <t>6,42; 9,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,67</t>
+          <t>6,94; 9,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,88</t>
+          <t>4,69; 6,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,77</t>
+          <t>7,12; 9,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,82</t>
+          <t>6,44; 8,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,96</t>
+          <t>5,48; 7,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,33</t>
+          <t>4,91; 7,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,37</t>
+          <t>7,52; 10,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,19</t>
+          <t>7,63; 10,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,2</t>
+          <t>6,64; 8,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,73</t>
+          <t>5,04; 6,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 9,7</t>
+          <t>7,78; 9,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,09</t>
+          <t>7,34; 9,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,17</t>
+          <t>6,31; 7,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,82</t>
+          <t>4,39; 8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 14,17</t>
+          <t>6,91; 13,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,65</t>
+          <t>5,17; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,76</t>
+          <t>6,26; 11,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,3</t>
+          <t>6,94; 12,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,75</t>
+          <t>5,42; 10,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,02</t>
+          <t>6,37; 11,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,99</t>
+          <t>5,83; 9,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,51</t>
+          <t>6,18; 9,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,26</t>
+          <t>6,76; 11,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,64</t>
+          <t>6,17; 9,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,63</t>
+          <t>6,51; 9,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,82</t>
+          <t>6,11; 7,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 10,52</t>
+          <t>8,43; 10,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,64</t>
+          <t>6,85; 8,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,74</t>
+          <t>6,25; 8,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,33</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,28</t>
+          <t>7,39; 9,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 9,28</t>
+          <t>7,35; 9,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,15</t>
+          <t>6,99; 8,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,33</t>
+          <t>6,1; 7,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,61</t>
+          <t>8,19; 9,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,71</t>
+          <t>7,34; 8,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,65</t>
+          <t>6,91; 8,15</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>112691</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77320; 114338</t>
+          <t>76882; 113805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89513; 128646</t>
+          <t>90767; 130335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50194; 81584</t>
+          <t>48389; 79950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32836; 57798</t>
+          <t>34824; 59718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59904; 93619</t>
+          <t>61637; 94412</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85372; 122903</t>
+          <t>83148; 125817</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53584; 89115</t>
+          <t>56325; 91454</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50284; 70994</t>
+          <t>55010; 79574</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147775; 198252</t>
+          <t>146899; 195368</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184892; 240175</t>
+          <t>187107; 241677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112383; 160747</t>
+          <t>112257; 158388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89390; 122347</t>
+          <t>96974; 131191</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128432</t>
+          <t>146949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>166252</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>313201</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79185; 116385</t>
+          <t>79314; 118368</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141078; 191512</t>
+          <t>139546; 193253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134523; 183039</t>
+          <t>133690; 185060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88216; 159361</t>
+          <t>122305; 177324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76831; 116428</t>
+          <t>77961; 115564</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132225; 181750</t>
+          <t>131807; 182265</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>150229; 202622</t>
+          <t>151658; 204625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111688; 183489</t>
+          <t>144148; 192084</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165116; 220626</t>
+          <t>165439; 221464</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>288682; 359910</t>
+          <t>288893; 356665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300804; 369405</t>
+          <t>298499; 369276</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>222308; 324686</t>
+          <t>277830; 347833</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56107</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>103648</t>
+          <t>114838</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24736; 48615</t>
+          <t>24221; 49435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35498; 68048</t>
+          <t>33203; 64688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28571; 52759</t>
+          <t>28273; 55256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41287; 76042</t>
+          <t>44550; 79728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32867; 58587</t>
+          <t>33081; 57800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25251; 49210</t>
+          <t>24785; 49557</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34574; 60511</t>
+          <t>35008; 60767</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38057; 59405</t>
+          <t>42850; 67414</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63950; 97701</t>
+          <t>63479; 99050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64918; 105654</t>
+          <t>63419; 104297</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69090; 105668</t>
+          <t>67660; 105486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84650; 125911</t>
+          <t>94204; 140025</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>260353</t>
+          <t>287061</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>488985</t>
+          <t>540730</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198803; 256265</t>
+          <t>200192; 258625</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>288083; 358811</t>
+          <t>287682; 360846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229394; 291825</t>
+          <t>231231; 294712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171959; 266946</t>
+          <t>220039; 288964</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>189238; 247559</t>
+          <t>190866; 247570</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>264385; 328642</t>
+          <t>261785; 331915</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>258571; 327784</t>
+          <t>259690; 327561</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>213948; 297209</t>
+          <t>260369; 318930</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>400407; 487562</t>
+          <t>405828; 486224</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>569642; 667944</t>
+          <t>569777; 666663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>509886; 601815</t>
+          <t>507048; 597849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>418744; 543066</t>
+          <t>500862; 590106</t>
         </is>
       </c>
     </row>
